--- a/Scout/waukee-vs-marshalltown-100226.xlsx
+++ b/Scout/waukee-vs-marshalltown-100226.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="Rd294ca49b7f3459b"/>
+    <sheet name="Sheet1" sheetId="1" r:id="R13eb75b161844cdd"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +58,21 @@
     <t>PASS ZONE</t>
   </si>
   <si>
+    <t>BACKFIELD</t>
+  </si>
+  <si>
+    <t>DEF FRONT</t>
+  </si>
+  <si>
+    <t>FRONT MOVEMENT</t>
+  </si>
+  <si>
+    <t>COVERAGE</t>
+  </si>
+  <si>
+    <t>BLITZ</t>
+  </si>
+  <si>
     <t>KICK YARDS</t>
   </si>
   <si>
@@ -79,9 +94,6 @@
     <t>MOTION DIR</t>
   </si>
   <si>
-    <t>COVERAGE</t>
-  </si>
-  <si>
     <t>SERIES</t>
   </si>
   <si>
@@ -115,6 +127,9 @@
     <t>Y</t>
   </si>
   <si>
+    <t>DOT UNDER</t>
+  </si>
+  <si>
     <t>BAL</t>
   </si>
   <si>
@@ -172,6 +187,9 @@
     <t>DOUBLE WING PRO</t>
   </si>
   <si>
+    <t>K DOT UNDER</t>
+  </si>
+  <si>
     <t>Y OFF OPEN</t>
   </si>
   <si>
@@ -184,18 +202,27 @@
     <t>SLANT</t>
   </si>
   <si>
+    <t>GUN STACK K</t>
+  </si>
+  <si>
     <t>TWINS OPEN</t>
   </si>
   <si>
     <t>GIVE @ 1</t>
   </si>
   <si>
+    <t>G TUCK DOT</t>
+  </si>
+  <si>
     <t>GIVE @ 2</t>
   </si>
   <si>
     <t>Rush, TD</t>
   </si>
   <si>
+    <t>GUN STACK G</t>
+  </si>
+  <si>
     <t>No Good</t>
   </si>
   <si>
@@ -211,6 +238,9 @@
     <t>Fair Catch</t>
   </si>
   <si>
+    <t>GUN EVEN</t>
+  </si>
+  <si>
     <t>TOWARD</t>
   </si>
   <si>
@@ -223,6 +253,9 @@
     <t>Incomplete</t>
   </si>
   <si>
+    <t>G</t>
+  </si>
+  <si>
     <t>Z SCREEN</t>
   </si>
   <si>
@@ -241,6 +274,9 @@
     <t>HB SWING</t>
   </si>
   <si>
+    <t>T UNDER</t>
+  </si>
+  <si>
     <t>SPLIT</t>
   </si>
   <si>
@@ -284,6 +320,9 @@
   </si>
   <si>
     <t>Out of Bounds</t>
+  </si>
+  <si>
+    <t>DOT</t>
   </si>
   <si>
     <t>TRIPS TIGHT BUNCH</t>
@@ -311,7 +350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y123"/>
+  <dimension ref="A1:AC123"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -389,6 +428,18 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -398,19 +449,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F2">
         <v>-40</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -421,7 +472,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -433,30 +484,33 @@
         <v>-23</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R3" t="s">
-        <v>34</v>
-      </c>
-      <c r="S3" t="s">
-        <v>35</v>
-      </c>
-      <c r="U3" t="s">
-        <v>36</v>
-      </c>
-      <c r="X3">
+        <v>37</v>
+      </c>
+      <c r="P3" t="s">
+        <v>38</v>
+      </c>
+      <c r="W3" t="s">
+        <v>39</v>
+      </c>
+      <c r="X3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB3">
         <v>1</v>
       </c>
     </row>
@@ -468,7 +522,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -480,30 +534,33 @@
         <v>-24</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J4">
         <v>10</v>
       </c>
       <c r="K4" t="s">
-        <v>37</v>
-      </c>
-      <c r="R4" t="s">
-        <v>34</v>
-      </c>
-      <c r="S4" t="s">
-        <v>35</v>
-      </c>
-      <c r="U4" t="s">
-        <v>26</v>
-      </c>
-      <c r="X4">
+        <v>42</v>
+      </c>
+      <c r="P4" t="s">
+        <v>38</v>
+      </c>
+      <c r="W4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB4">
         <v>1</v>
       </c>
     </row>
@@ -515,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -527,18 +584,18 @@
         <v>-34</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>33</v>
-      </c>
-      <c r="X5">
+        <v>37</v>
+      </c>
+      <c r="AB5">
         <v>1</v>
       </c>
     </row>
@@ -550,7 +607,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -562,30 +619,33 @@
         <v>-34</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J6">
         <v>-2</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
-      </c>
-      <c r="R6" t="s">
-        <v>34</v>
-      </c>
-      <c r="S6" t="s">
-        <v>35</v>
-      </c>
-      <c r="U6" t="s">
-        <v>36</v>
-      </c>
-      <c r="X6">
+        <v>37</v>
+      </c>
+      <c r="P6" t="s">
+        <v>38</v>
+      </c>
+      <c r="W6" t="s">
+        <v>39</v>
+      </c>
+      <c r="X6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB6">
         <v>1</v>
       </c>
     </row>
@@ -597,7 +657,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -609,30 +669,33 @@
         <v>-32</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J7">
         <v>-3</v>
       </c>
       <c r="K7" t="s">
-        <v>33</v>
-      </c>
-      <c r="R7" t="s">
-        <v>34</v>
-      </c>
-      <c r="S7" t="s">
-        <v>35</v>
-      </c>
-      <c r="U7" t="s">
-        <v>26</v>
-      </c>
-      <c r="X7">
+        <v>37</v>
+      </c>
+      <c r="P7" t="s">
+        <v>38</v>
+      </c>
+      <c r="W7" t="s">
+        <v>39</v>
+      </c>
+      <c r="X7" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB7">
         <v>1</v>
       </c>
     </row>
@@ -644,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -656,18 +719,18 @@
         <v>-29</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I8" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>33</v>
-      </c>
-      <c r="X8">
+        <v>37</v>
+      </c>
+      <c r="AB8">
         <v>1</v>
       </c>
     </row>
@@ -679,7 +742,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D9">
         <v>3</v>
@@ -691,30 +754,33 @@
         <v>-29</v>
       </c>
       <c r="G9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J9">
         <v>7</v>
       </c>
       <c r="K9" t="s">
-        <v>33</v>
-      </c>
-      <c r="R9" t="s">
-        <v>34</v>
-      </c>
-      <c r="S9" t="s">
-        <v>35</v>
-      </c>
-      <c r="U9" t="s">
-        <v>36</v>
-      </c>
-      <c r="X9">
+        <v>37</v>
+      </c>
+      <c r="P9" t="s">
+        <v>38</v>
+      </c>
+      <c r="W9" t="s">
+        <v>39</v>
+      </c>
+      <c r="X9" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB9">
         <v>1</v>
       </c>
     </row>
@@ -726,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D10">
         <v>4</v>
@@ -738,15 +804,15 @@
         <v>-36</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X10">
+        <v>45</v>
+      </c>
+      <c r="AB10">
         <v>1</v>
       </c>
     </row>
@@ -758,7 +824,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D11">
         <v>4</v>
@@ -767,15 +833,15 @@
         <v>-31</v>
       </c>
       <c r="G11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H11" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I11" t="s">
-        <v>41</v>
-      </c>
-      <c r="X11">
+        <v>46</v>
+      </c>
+      <c r="AB11">
         <v>1</v>
       </c>
     </row>
@@ -787,7 +853,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -799,33 +865,36 @@
         <v>-24</v>
       </c>
       <c r="G12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H12" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I12" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J12">
         <v>7</v>
       </c>
       <c r="K12" t="s">
-        <v>33</v>
-      </c>
-      <c r="R12" t="s">
-        <v>36</v>
-      </c>
-      <c r="S12" t="s">
-        <v>45</v>
-      </c>
-      <c r="T12" t="s">
-        <v>46</v>
-      </c>
-      <c r="U12" t="s">
-        <v>36</v>
-      </c>
-      <c r="X12">
+        <v>37</v>
+      </c>
+      <c r="P12" t="s">
+        <v>29</v>
+      </c>
+      <c r="W12" t="s">
+        <v>41</v>
+      </c>
+      <c r="X12" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB12">
         <v>1</v>
       </c>
     </row>
@@ -837,7 +906,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -849,33 +918,36 @@
         <v>-31</v>
       </c>
       <c r="G13" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H13" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I13" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="J13">
         <v>69</v>
       </c>
       <c r="K13" t="s">
-        <v>33</v>
-      </c>
-      <c r="R13" t="s">
-        <v>26</v>
-      </c>
-      <c r="S13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T13" t="s">
-        <v>48</v>
-      </c>
-      <c r="U13" t="s">
-        <v>36</v>
-      </c>
-      <c r="X13">
+        <v>37</v>
+      </c>
+      <c r="P13" t="s">
+        <v>29</v>
+      </c>
+      <c r="W13" t="s">
+        <v>30</v>
+      </c>
+      <c r="X13" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB13">
         <v>1</v>
       </c>
     </row>
@@ -887,21 +959,21 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F14">
         <v>3</v>
       </c>
       <c r="G14" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H14" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="I14" t="s">
-        <v>50</v>
-      </c>
-      <c r="X14">
+        <v>55</v>
+      </c>
+      <c r="AB14">
         <v>1</v>
       </c>
     </row>
@@ -913,19 +985,19 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F15">
         <v>-40</v>
       </c>
       <c r="G15" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H15" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I15" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -936,7 +1008,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -948,30 +1020,33 @@
         <v>-27</v>
       </c>
       <c r="G16" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H16" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I16" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>33</v>
-      </c>
-      <c r="R16" t="s">
-        <v>34</v>
-      </c>
-      <c r="S16" t="s">
-        <v>35</v>
-      </c>
-      <c r="U16" t="s">
-        <v>36</v>
-      </c>
-      <c r="X16">
+        <v>37</v>
+      </c>
+      <c r="P16" t="s">
+        <v>38</v>
+      </c>
+      <c r="W16" t="s">
+        <v>39</v>
+      </c>
+      <c r="X16" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB16">
         <v>2</v>
       </c>
     </row>
@@ -983,7 +1058,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -995,30 +1070,33 @@
         <v>-27</v>
       </c>
       <c r="G17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H17" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I17" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J17">
         <v>3</v>
       </c>
       <c r="K17" t="s">
-        <v>33</v>
-      </c>
-      <c r="R17" t="s">
-        <v>34</v>
-      </c>
-      <c r="S17" t="s">
-        <v>35</v>
-      </c>
-      <c r="U17" t="s">
-        <v>36</v>
-      </c>
-      <c r="X17">
+        <v>37</v>
+      </c>
+      <c r="P17" t="s">
+        <v>38</v>
+      </c>
+      <c r="W17" t="s">
+        <v>39</v>
+      </c>
+      <c r="X17" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB17">
         <v>2</v>
       </c>
     </row>
@@ -1030,7 +1108,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -1047,7 +1125,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -1059,30 +1137,33 @@
         <v>-30</v>
       </c>
       <c r="G19" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H19" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I19" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J19">
         <v>8</v>
       </c>
       <c r="K19" t="s">
-        <v>37</v>
-      </c>
-      <c r="R19" t="s">
-        <v>26</v>
-      </c>
-      <c r="S19" t="s">
-        <v>52</v>
-      </c>
-      <c r="U19" t="s">
-        <v>26</v>
-      </c>
-      <c r="X19">
+        <v>42</v>
+      </c>
+      <c r="P19" t="s">
+        <v>38</v>
+      </c>
+      <c r="W19" t="s">
+        <v>30</v>
+      </c>
+      <c r="X19" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB19">
         <v>2</v>
       </c>
     </row>
@@ -1094,7 +1175,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1106,30 +1187,33 @@
         <v>-38</v>
       </c>
       <c r="G20" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H20" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I20" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J20">
         <v>-2</v>
       </c>
       <c r="K20" t="s">
-        <v>33</v>
-      </c>
-      <c r="R20" t="s">
-        <v>26</v>
-      </c>
-      <c r="S20" t="s">
-        <v>52</v>
-      </c>
-      <c r="U20" t="s">
-        <v>26</v>
-      </c>
-      <c r="X20">
+        <v>37</v>
+      </c>
+      <c r="P20" t="s">
+        <v>38</v>
+      </c>
+      <c r="W20" t="s">
+        <v>30</v>
+      </c>
+      <c r="X20" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB20">
         <v>2</v>
       </c>
     </row>
@@ -1141,7 +1225,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -1153,30 +1237,33 @@
         <v>-36</v>
       </c>
       <c r="G21" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H21" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I21" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>33</v>
-      </c>
-      <c r="R21" t="s">
-        <v>36</v>
-      </c>
-      <c r="S21" t="s">
-        <v>52</v>
-      </c>
-      <c r="U21" t="s">
-        <v>26</v>
-      </c>
-      <c r="X21">
+        <v>37</v>
+      </c>
+      <c r="P21" t="s">
+        <v>38</v>
+      </c>
+      <c r="W21" t="s">
+        <v>41</v>
+      </c>
+      <c r="X21" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB21">
         <v>2</v>
       </c>
     </row>
@@ -1188,7 +1275,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D22">
         <v>3</v>
@@ -1200,30 +1287,33 @@
         <v>-36</v>
       </c>
       <c r="G22" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H22" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I22" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J22">
         <v>15</v>
       </c>
       <c r="K22" t="s">
-        <v>37</v>
-      </c>
-      <c r="R22" t="s">
-        <v>36</v>
-      </c>
-      <c r="S22" t="s">
-        <v>53</v>
-      </c>
-      <c r="U22" t="s">
-        <v>36</v>
-      </c>
-      <c r="X22">
+        <v>42</v>
+      </c>
+      <c r="P22" t="s">
+        <v>58</v>
+      </c>
+      <c r="W22" t="s">
+        <v>41</v>
+      </c>
+      <c r="X22" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB22">
         <v>2</v>
       </c>
     </row>
@@ -1235,7 +1325,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1247,30 +1337,33 @@
         <v>49</v>
       </c>
       <c r="G23" t="s">
+        <v>41</v>
+      </c>
+      <c r="H23" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" t="s">
         <v>36</v>
-      </c>
-      <c r="H23" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" t="s">
-        <v>32</v>
       </c>
       <c r="J23">
         <v>8</v>
       </c>
       <c r="K23" t="s">
-        <v>37</v>
-      </c>
-      <c r="R23" t="s">
-        <v>34</v>
-      </c>
-      <c r="S23" t="s">
-        <v>35</v>
-      </c>
-      <c r="U23" t="s">
-        <v>26</v>
-      </c>
-      <c r="X23">
+        <v>42</v>
+      </c>
+      <c r="P23" t="s">
+        <v>38</v>
+      </c>
+      <c r="W23" t="s">
+        <v>39</v>
+      </c>
+      <c r="X23" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB23">
         <v>2</v>
       </c>
     </row>
@@ -1282,7 +1375,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -1294,30 +1387,33 @@
         <v>41</v>
       </c>
       <c r="G24" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H24" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I24" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J24">
         <v>5</v>
       </c>
       <c r="K24" t="s">
-        <v>37</v>
-      </c>
-      <c r="R24" t="s">
-        <v>34</v>
-      </c>
-      <c r="S24" t="s">
-        <v>35</v>
-      </c>
-      <c r="U24" t="s">
-        <v>26</v>
-      </c>
-      <c r="X24">
+        <v>42</v>
+      </c>
+      <c r="P24" t="s">
+        <v>38</v>
+      </c>
+      <c r="W24" t="s">
+        <v>39</v>
+      </c>
+      <c r="X24" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB24">
         <v>2</v>
       </c>
     </row>
@@ -1329,7 +1425,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1341,30 +1437,33 @@
         <v>36</v>
       </c>
       <c r="G25" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H25" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I25" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>33</v>
-      </c>
-      <c r="R25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S25" t="s">
-        <v>35</v>
-      </c>
-      <c r="U25" t="s">
-        <v>36</v>
-      </c>
-      <c r="X25">
+        <v>37</v>
+      </c>
+      <c r="P25" t="s">
+        <v>38</v>
+      </c>
+      <c r="W25" t="s">
+        <v>39</v>
+      </c>
+      <c r="X25" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB25">
         <v>2</v>
       </c>
     </row>
@@ -1376,7 +1475,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -1388,30 +1487,33 @@
         <v>36</v>
       </c>
       <c r="G26" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H26" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I26" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J26">
         <v>15</v>
       </c>
       <c r="K26" t="s">
-        <v>33</v>
-      </c>
-      <c r="R26" t="s">
-        <v>34</v>
-      </c>
-      <c r="S26" t="s">
-        <v>35</v>
-      </c>
-      <c r="U26" t="s">
-        <v>36</v>
-      </c>
-      <c r="X26">
+        <v>37</v>
+      </c>
+      <c r="P26" t="s">
+        <v>38</v>
+      </c>
+      <c r="W26" t="s">
+        <v>39</v>
+      </c>
+      <c r="X26" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB26">
         <v>2</v>
       </c>
     </row>
@@ -1423,7 +1525,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1435,33 +1537,36 @@
         <v>-21</v>
       </c>
       <c r="G27" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H27" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I27" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J27">
         <v>12</v>
       </c>
       <c r="K27" t="s">
-        <v>33</v>
-      </c>
-      <c r="R27" t="s">
-        <v>36</v>
-      </c>
-      <c r="S27" t="s">
-        <v>55</v>
-      </c>
-      <c r="T27" t="s">
-        <v>56</v>
-      </c>
-      <c r="U27" t="s">
-        <v>26</v>
-      </c>
-      <c r="X27">
+        <v>37</v>
+      </c>
+      <c r="P27" t="s">
+        <v>29</v>
+      </c>
+      <c r="W27" t="s">
+        <v>41</v>
+      </c>
+      <c r="X27" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB27">
         <v>2</v>
       </c>
     </row>
@@ -1473,7 +1578,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -1485,33 +1590,36 @@
         <v>-33</v>
       </c>
       <c r="G28" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H28" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I28" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J28">
         <v>4</v>
       </c>
       <c r="K28" t="s">
-        <v>33</v>
-      </c>
-      <c r="R28" t="s">
-        <v>26</v>
-      </c>
-      <c r="S28" t="s">
-        <v>57</v>
-      </c>
-      <c r="T28" t="s">
-        <v>58</v>
-      </c>
-      <c r="U28" t="s">
-        <v>26</v>
-      </c>
-      <c r="X28">
+        <v>37</v>
+      </c>
+      <c r="P28" t="s">
+        <v>63</v>
+      </c>
+      <c r="W28" t="s">
+        <v>30</v>
+      </c>
+      <c r="X28" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB28">
         <v>2</v>
       </c>
     </row>
@@ -1523,7 +1631,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D29">
         <v>2</v>
@@ -1535,27 +1643,30 @@
         <v>-37</v>
       </c>
       <c r="G29" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I29" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J29">
         <v>-5</v>
       </c>
       <c r="K29" t="s">
-        <v>37</v>
-      </c>
-      <c r="R29" t="s">
-        <v>36</v>
-      </c>
-      <c r="S29" t="s">
-        <v>57</v>
-      </c>
-      <c r="T29" t="s">
-        <v>59</v>
-      </c>
-      <c r="X29">
+        <v>42</v>
+      </c>
+      <c r="P29" t="s">
+        <v>66</v>
+      </c>
+      <c r="W29" t="s">
+        <v>41</v>
+      </c>
+      <c r="X29" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB29">
         <v>2</v>
       </c>
     </row>
@@ -1567,7 +1678,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D30">
         <v>3</v>
@@ -1579,33 +1690,36 @@
         <v>-32</v>
       </c>
       <c r="G30" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H30" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I30" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="J30">
         <v>68</v>
       </c>
       <c r="K30" t="s">
-        <v>33</v>
-      </c>
-      <c r="R30" t="s">
-        <v>36</v>
-      </c>
-      <c r="S30" t="s">
-        <v>57</v>
-      </c>
-      <c r="T30" t="s">
-        <v>59</v>
-      </c>
-      <c r="U30" t="s">
-        <v>36</v>
-      </c>
-      <c r="X30">
+        <v>37</v>
+      </c>
+      <c r="P30" t="s">
+        <v>69</v>
+      </c>
+      <c r="W30" t="s">
+        <v>41</v>
+      </c>
+      <c r="X30" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB30">
         <v>2</v>
       </c>
     </row>
@@ -1617,21 +1731,21 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F31">
         <v>3</v>
       </c>
       <c r="G31" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H31" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="I31" t="s">
-        <v>61</v>
-      </c>
-      <c r="X31">
+        <v>70</v>
+      </c>
+      <c r="AB31">
         <v>2</v>
       </c>
     </row>
@@ -1643,19 +1757,19 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F32">
         <v>-40</v>
       </c>
       <c r="G32" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H32" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I32" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1780,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1678,30 +1792,33 @@
         <v>-24</v>
       </c>
       <c r="G33" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H33" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I33" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J33">
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>33</v>
-      </c>
-      <c r="R33" t="s">
-        <v>36</v>
-      </c>
-      <c r="S33" t="s">
-        <v>62</v>
-      </c>
-      <c r="U33" t="s">
-        <v>36</v>
-      </c>
-      <c r="X33">
+        <v>37</v>
+      </c>
+      <c r="P33" t="s">
+        <v>38</v>
+      </c>
+      <c r="W33" t="s">
+        <v>41</v>
+      </c>
+      <c r="X33" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB33">
         <v>3</v>
       </c>
     </row>
@@ -1713,7 +1830,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -1725,30 +1842,33 @@
         <v>-25</v>
       </c>
       <c r="G34" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H34" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I34" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J34">
         <v>8</v>
       </c>
       <c r="K34" t="s">
-        <v>37</v>
-      </c>
-      <c r="R34" t="s">
-        <v>26</v>
-      </c>
-      <c r="S34" t="s">
-        <v>63</v>
-      </c>
-      <c r="U34" t="s">
-        <v>26</v>
-      </c>
-      <c r="X34">
+        <v>42</v>
+      </c>
+      <c r="P34" t="s">
+        <v>38</v>
+      </c>
+      <c r="W34" t="s">
+        <v>30</v>
+      </c>
+      <c r="X34" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB34">
         <v>3</v>
       </c>
     </row>
@@ -1760,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D35">
         <v>3</v>
@@ -1772,30 +1892,33 @@
         <v>-33</v>
       </c>
       <c r="G35" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H35" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I35" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J35">
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>37</v>
-      </c>
-      <c r="R35" t="s">
-        <v>34</v>
-      </c>
-      <c r="S35" t="s">
-        <v>35</v>
-      </c>
-      <c r="U35" t="s">
-        <v>26</v>
-      </c>
-      <c r="X35">
+        <v>42</v>
+      </c>
+      <c r="P35" t="s">
+        <v>38</v>
+      </c>
+      <c r="W35" t="s">
+        <v>39</v>
+      </c>
+      <c r="X35" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB35">
         <v>3</v>
       </c>
     </row>
@@ -1807,7 +1930,7 @@
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1819,30 +1942,33 @@
         <v>-34</v>
       </c>
       <c r="G36" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H36" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I36" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J36">
         <v>-2</v>
       </c>
       <c r="K36" t="s">
-        <v>33</v>
-      </c>
-      <c r="R36" t="s">
-        <v>34</v>
-      </c>
-      <c r="S36" t="s">
-        <v>35</v>
-      </c>
-      <c r="U36" t="s">
-        <v>36</v>
-      </c>
-      <c r="X36">
+        <v>37</v>
+      </c>
+      <c r="P36" t="s">
+        <v>38</v>
+      </c>
+      <c r="W36" t="s">
+        <v>39</v>
+      </c>
+      <c r="X36" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB36">
         <v>3</v>
       </c>
     </row>
@@ -1854,7 +1980,7 @@
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D37">
         <v>2</v>
@@ -1866,30 +1992,33 @@
         <v>-32</v>
       </c>
       <c r="G37" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H37" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I37" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="J37">
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>33</v>
-      </c>
-      <c r="R37" t="s">
-        <v>26</v>
-      </c>
-      <c r="S37" t="s">
-        <v>52</v>
-      </c>
-      <c r="U37" t="s">
-        <v>36</v>
-      </c>
-      <c r="X37">
+        <v>37</v>
+      </c>
+      <c r="P37" t="s">
+        <v>38</v>
+      </c>
+      <c r="W37" t="s">
+        <v>30</v>
+      </c>
+      <c r="X37" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB37">
         <v>3</v>
       </c>
     </row>
@@ -1901,7 +2030,7 @@
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -1913,30 +2042,33 @@
         <v>-33</v>
       </c>
       <c r="G38" t="s">
+        <v>41</v>
+      </c>
+      <c r="H38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I38" t="s">
         <v>36</v>
-      </c>
-      <c r="H38" t="s">
-        <v>31</v>
-      </c>
-      <c r="I38" t="s">
-        <v>32</v>
       </c>
       <c r="J38">
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>33</v>
-      </c>
-      <c r="R38" t="s">
-        <v>26</v>
-      </c>
-      <c r="S38" t="s">
-        <v>52</v>
-      </c>
-      <c r="U38" t="s">
-        <v>26</v>
-      </c>
-      <c r="X38">
+        <v>37</v>
+      </c>
+      <c r="P38" t="s">
+        <v>38</v>
+      </c>
+      <c r="W38" t="s">
+        <v>30</v>
+      </c>
+      <c r="X38" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB38">
         <v>3</v>
       </c>
     </row>
@@ -1948,7 +2080,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D39">
         <v>4</v>
@@ -1960,15 +2092,15 @@
         <v>-33</v>
       </c>
       <c r="G39" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H39" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I39" t="s">
-        <v>65</v>
-      </c>
-      <c r="X39">
+        <v>74</v>
+      </c>
+      <c r="AB39">
         <v>3</v>
       </c>
     </row>
@@ -1980,7 +2112,7 @@
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1992,24 +2124,27 @@
         <v>-34</v>
       </c>
       <c r="G40" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I40" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J40">
         <v>-5</v>
       </c>
       <c r="K40" t="s">
-        <v>37</v>
-      </c>
-      <c r="R40" t="s">
-        <v>36</v>
-      </c>
-      <c r="S40" t="s">
-        <v>57</v>
-      </c>
-      <c r="X40">
+        <v>42</v>
+      </c>
+      <c r="P40" t="s">
+        <v>75</v>
+      </c>
+      <c r="W40" t="s">
+        <v>41</v>
+      </c>
+      <c r="X40" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB40">
         <v>3</v>
       </c>
     </row>
@@ -2021,7 +2156,7 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -2033,33 +2168,36 @@
         <v>-29</v>
       </c>
       <c r="G41" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H41" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I41" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J41">
         <v>6</v>
       </c>
       <c r="K41" t="s">
-        <v>33</v>
-      </c>
-      <c r="R41" t="s">
-        <v>36</v>
-      </c>
-      <c r="S41" t="s">
-        <v>57</v>
-      </c>
-      <c r="T41" t="s">
-        <v>66</v>
-      </c>
-      <c r="U41" t="s">
-        <v>36</v>
-      </c>
-      <c r="X41">
+        <v>37</v>
+      </c>
+      <c r="P41" t="s">
+        <v>75</v>
+      </c>
+      <c r="W41" t="s">
+        <v>41</v>
+      </c>
+      <c r="X41" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB41">
         <v>3</v>
       </c>
     </row>
@@ -2071,7 +2209,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -2083,36 +2221,39 @@
         <v>-35</v>
       </c>
       <c r="G42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H42" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I42" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J42">
         <v>10</v>
       </c>
       <c r="K42" t="s">
-        <v>33</v>
-      </c>
-      <c r="R42" t="s">
-        <v>36</v>
-      </c>
-      <c r="S42" t="s">
-        <v>57</v>
-      </c>
-      <c r="T42" t="s">
-        <v>67</v>
-      </c>
-      <c r="U42" t="s">
-        <v>36</v>
-      </c>
-      <c r="V42" t="s">
-        <v>36</v>
-      </c>
-      <c r="X42">
+        <v>37</v>
+      </c>
+      <c r="P42" t="s">
+        <v>75</v>
+      </c>
+      <c r="W42" t="s">
+        <v>41</v>
+      </c>
+      <c r="X42" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB42">
         <v>3</v>
       </c>
     </row>
@@ -2124,7 +2265,7 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -2136,36 +2277,39 @@
         <v>-45</v>
       </c>
       <c r="G43" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H43" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I43" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J43">
         <v>-10</v>
       </c>
       <c r="K43" t="s">
-        <v>37</v>
-      </c>
-      <c r="R43" t="s">
-        <v>26</v>
-      </c>
-      <c r="S43" t="s">
-        <v>57</v>
-      </c>
-      <c r="T43" t="s">
-        <v>68</v>
-      </c>
-      <c r="U43" t="s">
-        <v>36</v>
-      </c>
-      <c r="V43" t="s">
-        <v>26</v>
-      </c>
-      <c r="X43">
+        <v>42</v>
+      </c>
+      <c r="P43" t="s">
+        <v>75</v>
+      </c>
+      <c r="W43" t="s">
+        <v>30</v>
+      </c>
+      <c r="X43" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB43">
         <v>3</v>
       </c>
     </row>
@@ -2177,7 +2321,7 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -2189,36 +2333,39 @@
         <v>-35</v>
       </c>
       <c r="G44" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H44" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I44" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J44">
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>37</v>
-      </c>
-      <c r="R44" t="s">
-        <v>26</v>
-      </c>
-      <c r="S44" t="s">
-        <v>57</v>
-      </c>
-      <c r="T44" t="s">
-        <v>46</v>
-      </c>
-      <c r="U44" t="s">
-        <v>26</v>
-      </c>
-      <c r="V44" t="s">
-        <v>36</v>
-      </c>
-      <c r="X44">
+        <v>42</v>
+      </c>
+      <c r="P44" t="s">
+        <v>75</v>
+      </c>
+      <c r="W44" t="s">
+        <v>30</v>
+      </c>
+      <c r="X44" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB44">
         <v>3</v>
       </c>
     </row>
@@ -2230,7 +2377,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -2242,33 +2389,36 @@
         <v>-35</v>
       </c>
       <c r="G45" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H45" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I45" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J45">
         <v>-5</v>
       </c>
       <c r="K45" t="s">
-        <v>37</v>
-      </c>
-      <c r="R45" t="s">
-        <v>26</v>
-      </c>
-      <c r="S45" t="s">
-        <v>55</v>
-      </c>
-      <c r="T45" t="s">
-        <v>68</v>
-      </c>
-      <c r="U45" t="s">
-        <v>26</v>
-      </c>
-      <c r="X45">
+        <v>42</v>
+      </c>
+      <c r="P45" t="s">
+        <v>80</v>
+      </c>
+      <c r="W45" t="s">
+        <v>30</v>
+      </c>
+      <c r="X45" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB45">
         <v>3</v>
       </c>
     </row>
@@ -2280,7 +2430,7 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -2292,33 +2442,36 @@
         <v>-30</v>
       </c>
       <c r="G46" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H46" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I46" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J46">
         <v>18</v>
       </c>
       <c r="K46" t="s">
-        <v>33</v>
-      </c>
-      <c r="R46" t="s">
-        <v>26</v>
-      </c>
-      <c r="S46" t="s">
-        <v>63</v>
-      </c>
-      <c r="T46" t="s">
-        <v>70</v>
-      </c>
-      <c r="U46" t="s">
-        <v>26</v>
-      </c>
-      <c r="X46">
+        <v>37</v>
+      </c>
+      <c r="P46" t="s">
+        <v>80</v>
+      </c>
+      <c r="W46" t="s">
+        <v>30</v>
+      </c>
+      <c r="X46" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB46">
         <v>3</v>
       </c>
     </row>
@@ -2330,7 +2483,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D47">
         <v>3</v>
@@ -2342,33 +2495,36 @@
         <v>-48</v>
       </c>
       <c r="G47" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H47" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I47" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J47">
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>37</v>
-      </c>
-      <c r="R47" t="s">
-        <v>26</v>
-      </c>
-      <c r="S47" t="s">
-        <v>55</v>
-      </c>
-      <c r="T47" t="s">
-        <v>68</v>
-      </c>
-      <c r="U47" t="s">
-        <v>36</v>
-      </c>
-      <c r="X47">
+        <v>42</v>
+      </c>
+      <c r="P47" t="s">
+        <v>29</v>
+      </c>
+      <c r="W47" t="s">
+        <v>30</v>
+      </c>
+      <c r="X47" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB47">
         <v>3</v>
       </c>
     </row>
@@ -2380,7 +2536,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D48">
         <v>4</v>
@@ -2392,33 +2548,36 @@
         <v>-48</v>
       </c>
       <c r="G48" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H48" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I48" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J48">
         <v>10</v>
       </c>
       <c r="K48" t="s">
-        <v>33</v>
-      </c>
-      <c r="R48" t="s">
-        <v>26</v>
-      </c>
-      <c r="S48" t="s">
-        <v>45</v>
-      </c>
-      <c r="T48" t="s">
-        <v>46</v>
-      </c>
-      <c r="U48" t="s">
-        <v>36</v>
-      </c>
-      <c r="X48">
+        <v>37</v>
+      </c>
+      <c r="P48" t="s">
+        <v>29</v>
+      </c>
+      <c r="W48" t="s">
+        <v>30</v>
+      </c>
+      <c r="X48" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB48">
         <v>3</v>
       </c>
     </row>
@@ -2430,7 +2589,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -2442,33 +2601,36 @@
         <v>42</v>
       </c>
       <c r="G49" t="s">
+        <v>41</v>
+      </c>
+      <c r="H49" t="s">
+        <v>35</v>
+      </c>
+      <c r="I49" t="s">
         <v>36</v>
-      </c>
-      <c r="H49" t="s">
-        <v>31</v>
-      </c>
-      <c r="I49" t="s">
-        <v>32</v>
       </c>
       <c r="J49">
         <v>-1</v>
       </c>
       <c r="K49" t="s">
-        <v>37</v>
-      </c>
-      <c r="R49" t="s">
-        <v>26</v>
-      </c>
-      <c r="S49" t="s">
-        <v>57</v>
-      </c>
-      <c r="T49" t="s">
-        <v>58</v>
-      </c>
-      <c r="U49" t="s">
-        <v>26</v>
-      </c>
-      <c r="X49">
+        <v>42</v>
+      </c>
+      <c r="P49" t="s">
+        <v>69</v>
+      </c>
+      <c r="W49" t="s">
+        <v>30</v>
+      </c>
+      <c r="X49" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB49">
         <v>3</v>
       </c>
     </row>
@@ -2480,7 +2642,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -2492,33 +2654,36 @@
         <v>43</v>
       </c>
       <c r="G50" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H50" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I50" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J50">
         <v>7</v>
       </c>
       <c r="K50" t="s">
-        <v>33</v>
-      </c>
-      <c r="R50" t="s">
-        <v>26</v>
-      </c>
-      <c r="S50" t="s">
-        <v>71</v>
-      </c>
-      <c r="T50" t="s">
-        <v>72</v>
-      </c>
-      <c r="U50" t="s">
-        <v>26</v>
-      </c>
-      <c r="X50">
+        <v>37</v>
+      </c>
+      <c r="P50" t="s">
+        <v>29</v>
+      </c>
+      <c r="W50" t="s">
+        <v>30</v>
+      </c>
+      <c r="X50" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB50">
         <v>3</v>
       </c>
     </row>
@@ -2530,7 +2695,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D51">
         <v>3</v>
@@ -2542,33 +2707,36 @@
         <v>36</v>
       </c>
       <c r="G51" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H51" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I51" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J51">
         <v>5</v>
       </c>
       <c r="K51" t="s">
-        <v>33</v>
-      </c>
-      <c r="R51" t="s">
-        <v>36</v>
-      </c>
-      <c r="S51" t="s">
-        <v>63</v>
-      </c>
-      <c r="T51" t="s">
-        <v>73</v>
-      </c>
-      <c r="U51" t="s">
-        <v>26</v>
-      </c>
-      <c r="X51">
+        <v>37</v>
+      </c>
+      <c r="P51" t="s">
+        <v>80</v>
+      </c>
+      <c r="W51" t="s">
+        <v>41</v>
+      </c>
+      <c r="X51" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB51">
         <v>3</v>
       </c>
     </row>
@@ -2580,7 +2748,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2592,33 +2760,36 @@
         <v>31</v>
       </c>
       <c r="G52" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H52" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I52" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J52">
         <v>11</v>
       </c>
       <c r="K52" t="s">
-        <v>33</v>
-      </c>
-      <c r="R52" t="s">
-        <v>36</v>
-      </c>
-      <c r="S52" t="s">
-        <v>45</v>
-      </c>
-      <c r="T52" t="s">
-        <v>74</v>
-      </c>
-      <c r="U52" t="s">
-        <v>36</v>
-      </c>
-      <c r="X52">
+        <v>37</v>
+      </c>
+      <c r="P52" t="s">
+        <v>80</v>
+      </c>
+      <c r="W52" t="s">
+        <v>41</v>
+      </c>
+      <c r="X52" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB52">
         <v>3</v>
       </c>
     </row>
@@ -2630,7 +2801,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2642,33 +2813,36 @@
         <v>20</v>
       </c>
       <c r="G53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H53" t="s">
+        <v>35</v>
+      </c>
+      <c r="I53" t="s">
         <v>36</v>
-      </c>
-      <c r="H53" t="s">
-        <v>31</v>
-      </c>
-      <c r="I53" t="s">
-        <v>32</v>
       </c>
       <c r="J53">
         <v>7</v>
       </c>
       <c r="K53" t="s">
-        <v>33</v>
-      </c>
-      <c r="R53" t="s">
-        <v>26</v>
-      </c>
-      <c r="S53" t="s">
-        <v>57</v>
-      </c>
-      <c r="T53" t="s">
-        <v>59</v>
-      </c>
-      <c r="U53" t="s">
-        <v>36</v>
-      </c>
-      <c r="X53">
+        <v>37</v>
+      </c>
+      <c r="P53" t="s">
+        <v>63</v>
+      </c>
+      <c r="W53" t="s">
+        <v>30</v>
+      </c>
+      <c r="X53" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB53">
         <v>3</v>
       </c>
     </row>
@@ -2680,7 +2854,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D54">
         <v>2</v>
@@ -2692,33 +2866,36 @@
         <v>13</v>
       </c>
       <c r="G54" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H54" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I54" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J54">
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>37</v>
-      </c>
-      <c r="R54" t="s">
-        <v>26</v>
-      </c>
-      <c r="S54" t="s">
-        <v>63</v>
-      </c>
-      <c r="T54" t="s">
-        <v>75</v>
-      </c>
-      <c r="U54" t="s">
-        <v>26</v>
-      </c>
-      <c r="X54">
+        <v>42</v>
+      </c>
+      <c r="P54" t="s">
+        <v>80</v>
+      </c>
+      <c r="W54" t="s">
+        <v>30</v>
+      </c>
+      <c r="X54" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB54">
         <v>3</v>
       </c>
     </row>
@@ -2730,7 +2907,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D55">
         <v>3</v>
@@ -2742,33 +2919,36 @@
         <v>13</v>
       </c>
       <c r="G55" t="s">
+        <v>41</v>
+      </c>
+      <c r="H55" t="s">
+        <v>35</v>
+      </c>
+      <c r="I55" t="s">
         <v>36</v>
-      </c>
-      <c r="H55" t="s">
-        <v>31</v>
-      </c>
-      <c r="I55" t="s">
-        <v>32</v>
       </c>
       <c r="J55">
         <v>8</v>
       </c>
       <c r="K55" t="s">
-        <v>33</v>
-      </c>
-      <c r="R55" t="s">
-        <v>26</v>
-      </c>
-      <c r="S55" t="s">
-        <v>76</v>
-      </c>
-      <c r="T55" t="s">
-        <v>77</v>
-      </c>
-      <c r="U55" t="s">
-        <v>36</v>
-      </c>
-      <c r="X55">
+        <v>37</v>
+      </c>
+      <c r="P55" t="s">
+        <v>87</v>
+      </c>
+      <c r="W55" t="s">
+        <v>30</v>
+      </c>
+      <c r="X55" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB55">
         <v>3</v>
       </c>
     </row>
@@ -2780,7 +2960,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2792,33 +2972,36 @@
         <v>5</v>
       </c>
       <c r="G56" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H56" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I56" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="J56">
         <v>5</v>
       </c>
       <c r="K56" t="s">
-        <v>33</v>
-      </c>
-      <c r="R56" t="s">
-        <v>26</v>
-      </c>
-      <c r="S56" t="s">
-        <v>76</v>
-      </c>
-      <c r="T56" t="s">
-        <v>77</v>
-      </c>
-      <c r="U56" t="s">
-        <v>36</v>
-      </c>
-      <c r="X56">
+        <v>37</v>
+      </c>
+      <c r="P56" t="s">
+        <v>87</v>
+      </c>
+      <c r="W56" t="s">
+        <v>30</v>
+      </c>
+      <c r="X56" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB56">
         <v>3</v>
       </c>
     </row>
@@ -2830,21 +3013,21 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F57">
         <v>3</v>
       </c>
       <c r="G57" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H57" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="I57" t="s">
-        <v>50</v>
-      </c>
-      <c r="X57">
+        <v>55</v>
+      </c>
+      <c r="AB57">
         <v>3</v>
       </c>
     </row>
@@ -2856,19 +3039,19 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F58">
         <v>-40</v>
       </c>
       <c r="G58" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H58" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I58" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59">
@@ -2879,7 +3062,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2891,30 +3074,33 @@
         <v>-35</v>
       </c>
       <c r="G59" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H59" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I59" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J59">
         <v>-20</v>
       </c>
       <c r="K59" t="s">
-        <v>33</v>
-      </c>
-      <c r="R59" t="s">
-        <v>36</v>
-      </c>
-      <c r="S59" t="s">
-        <v>52</v>
-      </c>
-      <c r="U59" t="s">
-        <v>36</v>
-      </c>
-      <c r="X59">
+        <v>37</v>
+      </c>
+      <c r="P59" t="s">
+        <v>38</v>
+      </c>
+      <c r="W59" t="s">
+        <v>41</v>
+      </c>
+      <c r="X59" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB59">
         <v>4</v>
       </c>
     </row>
@@ -2926,7 +3112,7 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D60">
         <v>2</v>
@@ -2938,30 +3124,33 @@
         <v>-15</v>
       </c>
       <c r="G60" t="s">
+        <v>41</v>
+      </c>
+      <c r="H60" t="s">
+        <v>35</v>
+      </c>
+      <c r="I60" t="s">
         <v>36</v>
-      </c>
-      <c r="H60" t="s">
-        <v>31</v>
-      </c>
-      <c r="I60" t="s">
-        <v>32</v>
       </c>
       <c r="J60">
         <v>11</v>
       </c>
       <c r="K60" t="s">
-        <v>33</v>
-      </c>
-      <c r="R60" t="s">
-        <v>34</v>
-      </c>
-      <c r="S60" t="s">
-        <v>35</v>
-      </c>
-      <c r="U60" t="s">
-        <v>26</v>
-      </c>
-      <c r="X60">
+        <v>37</v>
+      </c>
+      <c r="P60" t="s">
+        <v>38</v>
+      </c>
+      <c r="W60" t="s">
+        <v>39</v>
+      </c>
+      <c r="X60" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB60">
         <v>4</v>
       </c>
     </row>
@@ -2973,7 +3162,7 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D61">
         <v>3</v>
@@ -2985,30 +3174,33 @@
         <v>-26</v>
       </c>
       <c r="G61" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H61" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I61" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J61">
         <v>-1</v>
       </c>
       <c r="K61" t="s">
-        <v>33</v>
-      </c>
-      <c r="R61" t="s">
-        <v>34</v>
-      </c>
-      <c r="S61" t="s">
-        <v>35</v>
-      </c>
-      <c r="U61" t="s">
-        <v>36</v>
-      </c>
-      <c r="X61">
+        <v>37</v>
+      </c>
+      <c r="P61" t="s">
+        <v>38</v>
+      </c>
+      <c r="W61" t="s">
+        <v>39</v>
+      </c>
+      <c r="X61" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB61">
         <v>4</v>
       </c>
     </row>
@@ -3020,7 +3212,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D62">
         <v>4</v>
@@ -3032,15 +3224,15 @@
         <v>-25</v>
       </c>
       <c r="G62" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H62" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I62" t="s">
-        <v>41</v>
-      </c>
-      <c r="X62">
+        <v>46</v>
+      </c>
+      <c r="AB62">
         <v>4</v>
       </c>
     </row>
@@ -3052,7 +3244,7 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -3064,33 +3256,36 @@
         <v>45</v>
       </c>
       <c r="G63" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H63" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I63" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="J63">
         <v>45</v>
       </c>
       <c r="K63" t="s">
-        <v>33</v>
-      </c>
-      <c r="R63" t="s">
-        <v>36</v>
-      </c>
-      <c r="S63" t="s">
-        <v>79</v>
-      </c>
-      <c r="T63" t="s">
+        <v>37</v>
+      </c>
+      <c r="P63" t="s">
         <v>80</v>
       </c>
-      <c r="U63" t="s">
-        <v>36</v>
-      </c>
-      <c r="X63">
+      <c r="W63" t="s">
+        <v>41</v>
+      </c>
+      <c r="X63" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB63">
         <v>4</v>
       </c>
     </row>
@@ -3102,21 +3297,21 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F64">
         <v>3</v>
       </c>
       <c r="G64" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H64" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="I64" t="s">
-        <v>50</v>
-      </c>
-      <c r="X64">
+        <v>55</v>
+      </c>
+      <c r="AB64">
         <v>4</v>
       </c>
     </row>
@@ -3128,19 +3323,19 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F65">
         <v>-40</v>
       </c>
       <c r="G65" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H65" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I65" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="66">
@@ -3151,7 +3346,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -3163,30 +3358,33 @@
         <v>-13</v>
       </c>
       <c r="G66" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H66" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I66" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J66">
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>33</v>
-      </c>
-      <c r="R66" t="s">
-        <v>36</v>
-      </c>
-      <c r="S66" t="s">
-        <v>52</v>
-      </c>
-      <c r="U66" t="s">
-        <v>26</v>
-      </c>
-      <c r="X66">
+        <v>37</v>
+      </c>
+      <c r="P66" t="s">
+        <v>38</v>
+      </c>
+      <c r="W66" t="s">
+        <v>41</v>
+      </c>
+      <c r="X66" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB66">
         <v>5</v>
       </c>
     </row>
@@ -3198,7 +3396,7 @@
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D67">
         <v>2</v>
@@ -3210,30 +3408,33 @@
         <v>-13</v>
       </c>
       <c r="G67" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H67" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I67" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J67">
         <v>12</v>
       </c>
       <c r="K67" t="s">
-        <v>37</v>
-      </c>
-      <c r="R67" t="s">
-        <v>34</v>
-      </c>
-      <c r="S67" t="s">
-        <v>81</v>
-      </c>
-      <c r="U67" t="s">
-        <v>26</v>
-      </c>
-      <c r="X67">
+        <v>42</v>
+      </c>
+      <c r="P67" t="s">
+        <v>38</v>
+      </c>
+      <c r="W67" t="s">
+        <v>39</v>
+      </c>
+      <c r="X67" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB67">
         <v>5</v>
       </c>
     </row>
@@ -3245,7 +3446,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -3257,30 +3458,33 @@
         <v>-25</v>
       </c>
       <c r="G68" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H68" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I68" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J68">
         <v>8</v>
       </c>
       <c r="K68" t="s">
-        <v>37</v>
-      </c>
-      <c r="R68" t="s">
-        <v>26</v>
-      </c>
-      <c r="S68" t="s">
-        <v>52</v>
-      </c>
-      <c r="U68" t="s">
-        <v>36</v>
-      </c>
-      <c r="X68">
+        <v>42</v>
+      </c>
+      <c r="P68" t="s">
+        <v>38</v>
+      </c>
+      <c r="W68" t="s">
+        <v>30</v>
+      </c>
+      <c r="X68" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB68">
         <v>5</v>
       </c>
     </row>
@@ -3292,7 +3496,7 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D69">
         <v>2</v>
@@ -3304,30 +3508,33 @@
         <v>-33</v>
       </c>
       <c r="G69" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H69" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I69" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J69">
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>33</v>
-      </c>
-      <c r="R69" t="s">
-        <v>34</v>
-      </c>
-      <c r="S69" t="s">
-        <v>35</v>
-      </c>
-      <c r="U69" t="s">
-        <v>36</v>
-      </c>
-      <c r="X69">
+        <v>37</v>
+      </c>
+      <c r="P69" t="s">
+        <v>38</v>
+      </c>
+      <c r="W69" t="s">
+        <v>39</v>
+      </c>
+      <c r="X69" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB69">
         <v>5</v>
       </c>
     </row>
@@ -3339,7 +3546,7 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D70">
         <v>3</v>
@@ -3351,18 +3558,18 @@
         <v>-33</v>
       </c>
       <c r="G70" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I70" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J70">
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>33</v>
-      </c>
-      <c r="X70">
+        <v>37</v>
+      </c>
+      <c r="AB70">
         <v>5</v>
       </c>
     </row>
@@ -3374,7 +3581,7 @@
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D71">
         <v>3</v>
@@ -3386,30 +3593,33 @@
         <v>-33</v>
       </c>
       <c r="G71" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H71" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I71" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J71">
         <v>-7</v>
       </c>
       <c r="K71" t="s">
-        <v>33</v>
-      </c>
-      <c r="R71" t="s">
-        <v>36</v>
-      </c>
-      <c r="S71" t="s">
-        <v>52</v>
-      </c>
-      <c r="U71" t="s">
-        <v>26</v>
-      </c>
-      <c r="X71">
+        <v>37</v>
+      </c>
+      <c r="P71" t="s">
+        <v>38</v>
+      </c>
+      <c r="W71" t="s">
+        <v>41</v>
+      </c>
+      <c r="X71" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB71">
         <v>5</v>
       </c>
     </row>
@@ -3421,7 +3631,7 @@
         <v>3</v>
       </c>
       <c r="C72" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D72">
         <v>4</v>
@@ -3433,13 +3643,13 @@
         <v>-40</v>
       </c>
       <c r="G72" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H72" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I72" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="73">
@@ -3450,7 +3660,7 @@
         <v>3</v>
       </c>
       <c r="C73" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -3462,36 +3672,39 @@
         <v>-40</v>
       </c>
       <c r="G73" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H73" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I73" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J73">
         <v>8</v>
       </c>
       <c r="K73" t="s">
-        <v>33</v>
-      </c>
-      <c r="R73" t="s">
-        <v>26</v>
-      </c>
-      <c r="S73" t="s">
-        <v>63</v>
-      </c>
-      <c r="T73" t="s">
-        <v>83</v>
-      </c>
-      <c r="U73" t="s">
-        <v>36</v>
-      </c>
-      <c r="V73" t="s">
-        <v>36</v>
-      </c>
-      <c r="X73">
+        <v>37</v>
+      </c>
+      <c r="P73" t="s">
+        <v>29</v>
+      </c>
+      <c r="W73" t="s">
+        <v>30</v>
+      </c>
+      <c r="X73" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA73" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB73">
         <v>4</v>
       </c>
     </row>
@@ -3503,7 +3716,7 @@
         <v>3</v>
       </c>
       <c r="C74" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D74">
         <v>2</v>
@@ -3515,36 +3728,39 @@
         <v>-48</v>
       </c>
       <c r="G74" t="s">
+        <v>41</v>
+      </c>
+      <c r="H74" t="s">
+        <v>35</v>
+      </c>
+      <c r="I74" t="s">
         <v>36</v>
-      </c>
-      <c r="H74" t="s">
-        <v>31</v>
-      </c>
-      <c r="I74" t="s">
-        <v>32</v>
       </c>
       <c r="J74">
         <v>4</v>
       </c>
       <c r="K74" t="s">
-        <v>33</v>
-      </c>
-      <c r="R74" t="s">
-        <v>36</v>
-      </c>
-      <c r="S74" t="s">
+        <v>37</v>
+      </c>
+      <c r="P74" t="s">
+        <v>80</v>
+      </c>
+      <c r="W74" t="s">
+        <v>41</v>
+      </c>
+      <c r="X74" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y74" t="s">
         <v>84</v>
       </c>
-      <c r="T74" t="s">
-        <v>73</v>
-      </c>
-      <c r="U74" t="s">
-        <v>26</v>
-      </c>
-      <c r="V74" t="s">
-        <v>36</v>
-      </c>
-      <c r="X74">
+      <c r="Z74" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA74" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB74">
         <v>4</v>
       </c>
     </row>
@@ -3556,7 +3772,7 @@
         <v>3</v>
       </c>
       <c r="C75" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3568,33 +3784,36 @@
         <v>48</v>
       </c>
       <c r="G75" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H75" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I75" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J75">
         <v>34</v>
       </c>
       <c r="K75" t="s">
-        <v>33</v>
-      </c>
-      <c r="R75" t="s">
-        <v>36</v>
-      </c>
-      <c r="S75" t="s">
-        <v>55</v>
-      </c>
-      <c r="T75" t="s">
-        <v>68</v>
-      </c>
-      <c r="U75" t="s">
-        <v>26</v>
-      </c>
-      <c r="X75">
+        <v>37</v>
+      </c>
+      <c r="P75" t="s">
+        <v>29</v>
+      </c>
+      <c r="W75" t="s">
+        <v>41</v>
+      </c>
+      <c r="X75" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB75">
         <v>4</v>
       </c>
     </row>
@@ -3606,7 +3825,7 @@
         <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -3618,33 +3837,36 @@
         <v>14</v>
       </c>
       <c r="G76" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H76" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I76" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="J76">
         <v>14</v>
       </c>
       <c r="K76" t="s">
-        <v>33</v>
-      </c>
-      <c r="R76" t="s">
-        <v>36</v>
-      </c>
-      <c r="S76" t="s">
-        <v>71</v>
-      </c>
-      <c r="T76" t="s">
-        <v>85</v>
-      </c>
-      <c r="U76" t="s">
-        <v>26</v>
-      </c>
-      <c r="X76">
+        <v>37</v>
+      </c>
+      <c r="P76" t="s">
+        <v>80</v>
+      </c>
+      <c r="W76" t="s">
+        <v>41</v>
+      </c>
+      <c r="X76" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB76">
         <v>4</v>
       </c>
     </row>
@@ -3656,21 +3878,21 @@
         <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F77">
         <v>3</v>
       </c>
       <c r="G77" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H77" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="I77" t="s">
-        <v>50</v>
-      </c>
-      <c r="X77">
+        <v>55</v>
+      </c>
+      <c r="AB77">
         <v>4</v>
       </c>
     </row>
@@ -3682,19 +3904,19 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F78">
         <v>-40</v>
       </c>
       <c r="G78" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H78" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I78" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79">
@@ -3705,7 +3927,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3717,30 +3939,33 @@
         <v>-10</v>
       </c>
       <c r="G79" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H79" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I79" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J79">
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>33</v>
-      </c>
-      <c r="R79" t="s">
-        <v>36</v>
-      </c>
-      <c r="S79" t="s">
-        <v>52</v>
-      </c>
-      <c r="U79" t="s">
-        <v>26</v>
-      </c>
-      <c r="X79">
+        <v>37</v>
+      </c>
+      <c r="P79" t="s">
+        <v>38</v>
+      </c>
+      <c r="W79" t="s">
+        <v>41</v>
+      </c>
+      <c r="X79" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB79">
         <v>6</v>
       </c>
     </row>
@@ -3752,7 +3977,7 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D80">
         <v>2</v>
@@ -3764,30 +3989,33 @@
         <v>-11</v>
       </c>
       <c r="G80" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H80" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I80" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J80">
         <v>9</v>
       </c>
       <c r="K80" t="s">
-        <v>37</v>
-      </c>
-      <c r="R80" t="s">
-        <v>36</v>
-      </c>
-      <c r="S80" t="s">
-        <v>52</v>
-      </c>
-      <c r="U80" t="s">
-        <v>36</v>
-      </c>
-      <c r="X80">
+        <v>42</v>
+      </c>
+      <c r="P80" t="s">
+        <v>38</v>
+      </c>
+      <c r="W80" t="s">
+        <v>41</v>
+      </c>
+      <c r="X80" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB80">
         <v>6</v>
       </c>
     </row>
@@ -3799,7 +4027,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -3811,30 +4039,33 @@
         <v>-20</v>
       </c>
       <c r="G81" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H81" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I81" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J81">
         <v>7</v>
       </c>
       <c r="K81" t="s">
-        <v>37</v>
-      </c>
-      <c r="R81" t="s">
-        <v>36</v>
-      </c>
-      <c r="S81" t="s">
-        <v>52</v>
-      </c>
-      <c r="U81" t="s">
-        <v>26</v>
-      </c>
-      <c r="X81">
+        <v>42</v>
+      </c>
+      <c r="P81" t="s">
+        <v>38</v>
+      </c>
+      <c r="W81" t="s">
+        <v>41</v>
+      </c>
+      <c r="X81" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB81">
         <v>6</v>
       </c>
     </row>
@@ -3846,7 +4077,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D82">
         <v>2</v>
@@ -3858,33 +4089,36 @@
         <v>-27</v>
       </c>
       <c r="G82" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H82" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I82" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J82">
         <v>2</v>
       </c>
       <c r="K82" t="s">
-        <v>37</v>
-      </c>
-      <c r="R82" t="s">
-        <v>26</v>
-      </c>
-      <c r="S82" t="s">
-        <v>52</v>
-      </c>
-      <c r="U82" t="s">
-        <v>36</v>
-      </c>
-      <c r="V82" t="s">
-        <v>36</v>
-      </c>
-      <c r="X82">
+        <v>42</v>
+      </c>
+      <c r="P82" t="s">
+        <v>38</v>
+      </c>
+      <c r="W82" t="s">
+        <v>30</v>
+      </c>
+      <c r="X82" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA82" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB82">
         <v>6</v>
       </c>
     </row>
@@ -3896,7 +4130,7 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D83">
         <v>3</v>
@@ -3908,18 +4142,18 @@
         <v>-29</v>
       </c>
       <c r="G83" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I83" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J83">
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>33</v>
-      </c>
-      <c r="X83">
+        <v>37</v>
+      </c>
+      <c r="AB83">
         <v>6</v>
       </c>
     </row>
@@ -3931,7 +4165,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D84">
         <v>3</v>
@@ -3943,24 +4177,27 @@
         <v>-29</v>
       </c>
       <c r="G84" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I84" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J84">
         <v>-5</v>
       </c>
       <c r="K84" t="s">
-        <v>33</v>
-      </c>
-      <c r="R84" t="s">
-        <v>36</v>
-      </c>
-      <c r="S84" t="s">
-        <v>62</v>
-      </c>
-      <c r="X84">
+        <v>37</v>
+      </c>
+      <c r="P84" t="s">
+        <v>38</v>
+      </c>
+      <c r="W84" t="s">
+        <v>41</v>
+      </c>
+      <c r="X84" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB84">
         <v>6</v>
       </c>
     </row>
@@ -3972,7 +4209,7 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D85">
         <v>4</v>
@@ -3984,30 +4221,33 @@
         <v>-24</v>
       </c>
       <c r="G85" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H85" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I85" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J85">
         <v>4</v>
       </c>
       <c r="K85" t="s">
-        <v>33</v>
-      </c>
-      <c r="R85" t="s">
-        <v>36</v>
-      </c>
-      <c r="S85" t="s">
-        <v>86</v>
-      </c>
-      <c r="U85" t="s">
-        <v>36</v>
-      </c>
-      <c r="X85">
+        <v>37</v>
+      </c>
+      <c r="P85" t="s">
+        <v>38</v>
+      </c>
+      <c r="W85" t="s">
+        <v>41</v>
+      </c>
+      <c r="X85" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB85">
         <v>6</v>
       </c>
     </row>
@@ -4019,7 +4259,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -4031,15 +4271,15 @@
         <v>-28</v>
       </c>
       <c r="G86" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H86" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I86" t="s">
-        <v>28</v>
-      </c>
-      <c r="X86">
+        <v>32</v>
+      </c>
+      <c r="AB86">
         <v>6</v>
       </c>
     </row>
@@ -4051,7 +4291,7 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -4063,33 +4303,36 @@
         <v>-38</v>
       </c>
       <c r="G87" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H87" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I87" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J87">
         <v>4</v>
       </c>
       <c r="K87" t="s">
-        <v>33</v>
-      </c>
-      <c r="R87" t="s">
-        <v>36</v>
-      </c>
-      <c r="S87" t="s">
-        <v>45</v>
-      </c>
-      <c r="T87" t="s">
-        <v>72</v>
-      </c>
-      <c r="U87" t="s">
-        <v>26</v>
-      </c>
-      <c r="X87">
+        <v>37</v>
+      </c>
+      <c r="P87" t="s">
+        <v>29</v>
+      </c>
+      <c r="W87" t="s">
+        <v>41</v>
+      </c>
+      <c r="X87" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB87">
         <v>5</v>
       </c>
     </row>
@@ -4101,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D88">
         <v>2</v>
@@ -4113,33 +4356,36 @@
         <v>-42</v>
       </c>
       <c r="G88" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H88" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I88" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J88">
         <v>1</v>
       </c>
       <c r="K88" t="s">
-        <v>37</v>
-      </c>
-      <c r="R88" t="s">
-        <v>36</v>
-      </c>
-      <c r="S88" t="s">
-        <v>87</v>
-      </c>
-      <c r="T88" t="s">
-        <v>66</v>
-      </c>
-      <c r="U88" t="s">
-        <v>36</v>
-      </c>
-      <c r="X88">
+        <v>42</v>
+      </c>
+      <c r="P88" t="s">
+        <v>29</v>
+      </c>
+      <c r="W88" t="s">
+        <v>41</v>
+      </c>
+      <c r="X88" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB88">
         <v>5</v>
       </c>
     </row>
@@ -4151,7 +4397,7 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D89">
         <v>3</v>
@@ -4163,27 +4409,30 @@
         <v>-43</v>
       </c>
       <c r="G89" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I89" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J89">
         <v>-5</v>
       </c>
       <c r="K89" t="s">
-        <v>37</v>
-      </c>
-      <c r="R89" t="s">
-        <v>36</v>
-      </c>
-      <c r="S89" t="s">
-        <v>45</v>
-      </c>
-      <c r="T89" t="s">
-        <v>46</v>
-      </c>
-      <c r="X89">
+        <v>42</v>
+      </c>
+      <c r="P89" t="s">
+        <v>29</v>
+      </c>
+      <c r="W89" t="s">
+        <v>41</v>
+      </c>
+      <c r="X89" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB89">
         <v>5</v>
       </c>
     </row>
@@ -4195,7 +4444,7 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D90">
         <v>3</v>
@@ -4207,33 +4456,36 @@
         <v>-38</v>
       </c>
       <c r="G90" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H90" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I90" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J90">
         <v>11</v>
       </c>
       <c r="K90" t="s">
-        <v>33</v>
-      </c>
-      <c r="R90" t="s">
-        <v>36</v>
-      </c>
-      <c r="S90" t="s">
-        <v>63</v>
-      </c>
-      <c r="T90" t="s">
-        <v>70</v>
-      </c>
-      <c r="U90" t="s">
-        <v>36</v>
-      </c>
-      <c r="X90">
+        <v>37</v>
+      </c>
+      <c r="P90" t="s">
+        <v>80</v>
+      </c>
+      <c r="W90" t="s">
+        <v>41</v>
+      </c>
+      <c r="X90" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB90">
         <v>5</v>
       </c>
     </row>
@@ -4245,7 +4497,7 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -4257,33 +4509,36 @@
         <v>-49</v>
       </c>
       <c r="G91" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H91" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I91" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J91">
         <v>3</v>
       </c>
       <c r="K91" t="s">
-        <v>37</v>
-      </c>
-      <c r="R91" t="s">
-        <v>26</v>
-      </c>
-      <c r="S91" t="s">
-        <v>84</v>
-      </c>
-      <c r="T91" t="s">
-        <v>88</v>
-      </c>
-      <c r="U91" t="s">
-        <v>26</v>
-      </c>
-      <c r="X91">
+        <v>42</v>
+      </c>
+      <c r="P91" t="s">
+        <v>29</v>
+      </c>
+      <c r="W91" t="s">
+        <v>30</v>
+      </c>
+      <c r="X91" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB91">
         <v>5</v>
       </c>
     </row>
@@ -4295,7 +4550,7 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D92">
         <v>2</v>
@@ -4307,18 +4562,18 @@
         <v>48</v>
       </c>
       <c r="G92" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I92" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J92">
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>37</v>
-      </c>
-      <c r="X92">
+        <v>42</v>
+      </c>
+      <c r="AB92">
         <v>5</v>
       </c>
     </row>
@@ -4330,7 +4585,7 @@
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D93">
         <v>2</v>
@@ -4342,33 +4597,36 @@
         <v>48</v>
       </c>
       <c r="G93" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H93" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I93" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="J93">
         <v>48</v>
       </c>
       <c r="K93" t="s">
-        <v>33</v>
-      </c>
-      <c r="R93" t="s">
-        <v>36</v>
-      </c>
-      <c r="S93" t="s">
-        <v>45</v>
-      </c>
-      <c r="T93" t="s">
-        <v>89</v>
-      </c>
-      <c r="U93" t="s">
-        <v>36</v>
-      </c>
-      <c r="X93">
+        <v>37</v>
+      </c>
+      <c r="P93" t="s">
+        <v>80</v>
+      </c>
+      <c r="W93" t="s">
+        <v>41</v>
+      </c>
+      <c r="X93" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB93">
         <v>5</v>
       </c>
     </row>
@@ -4380,21 +4638,21 @@
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F94">
         <v>3</v>
       </c>
       <c r="G94" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H94" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="I94" t="s">
-        <v>50</v>
-      </c>
-      <c r="X94">
+        <v>55</v>
+      </c>
+      <c r="AB94">
         <v>5</v>
       </c>
     </row>
@@ -4406,19 +4664,19 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F95">
         <v>-40</v>
       </c>
       <c r="G95" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H95" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I95" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="96">
@@ -4429,7 +4687,7 @@
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -4441,30 +4699,33 @@
         <v>-19</v>
       </c>
       <c r="G96" t="s">
+        <v>41</v>
+      </c>
+      <c r="H96" t="s">
+        <v>35</v>
+      </c>
+      <c r="I96" t="s">
         <v>36</v>
-      </c>
-      <c r="H96" t="s">
-        <v>31</v>
-      </c>
-      <c r="I96" t="s">
-        <v>32</v>
       </c>
       <c r="J96">
         <v>12</v>
       </c>
       <c r="K96" t="s">
-        <v>37</v>
-      </c>
-      <c r="R96" t="s">
-        <v>26</v>
-      </c>
-      <c r="S96" t="s">
-        <v>63</v>
-      </c>
-      <c r="U96" t="s">
-        <v>26</v>
-      </c>
-      <c r="X96">
+        <v>42</v>
+      </c>
+      <c r="P96" t="s">
+        <v>38</v>
+      </c>
+      <c r="W96" t="s">
+        <v>30</v>
+      </c>
+      <c r="X96" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB96">
         <v>7</v>
       </c>
     </row>
@@ -4476,7 +4737,7 @@
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -4488,30 +4749,33 @@
         <v>-31</v>
       </c>
       <c r="G97" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H97" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I97" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J97">
         <v>4</v>
       </c>
       <c r="K97" t="s">
-        <v>37</v>
-      </c>
-      <c r="R97" t="s">
-        <v>34</v>
-      </c>
-      <c r="S97" t="s">
-        <v>35</v>
-      </c>
-      <c r="U97" t="s">
-        <v>36</v>
-      </c>
-      <c r="X97">
+        <v>42</v>
+      </c>
+      <c r="P97" t="s">
+        <v>38</v>
+      </c>
+      <c r="W97" t="s">
+        <v>39</v>
+      </c>
+      <c r="X97" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB97">
         <v>7</v>
       </c>
     </row>
@@ -4523,7 +4787,7 @@
         <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D98">
         <v>2</v>
@@ -4535,30 +4799,33 @@
         <v>-35</v>
       </c>
       <c r="G98" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H98" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I98" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J98">
         <v>-8</v>
       </c>
       <c r="K98" t="s">
-        <v>33</v>
-      </c>
-      <c r="R98" t="s">
-        <v>26</v>
-      </c>
-      <c r="S98" t="s">
-        <v>63</v>
-      </c>
-      <c r="U98" t="s">
-        <v>26</v>
-      </c>
-      <c r="X98">
+        <v>37</v>
+      </c>
+      <c r="P98" t="s">
+        <v>38</v>
+      </c>
+      <c r="W98" t="s">
+        <v>30</v>
+      </c>
+      <c r="X98" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB98">
         <v>7</v>
       </c>
     </row>
@@ -4570,7 +4837,7 @@
         <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D99">
         <v>3</v>
@@ -4582,30 +4849,33 @@
         <v>-27</v>
       </c>
       <c r="G99" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H99" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I99" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J99">
         <v>5</v>
       </c>
       <c r="K99" t="s">
-        <v>33</v>
-      </c>
-      <c r="R99" t="s">
-        <v>36</v>
-      </c>
-      <c r="S99" t="s">
-        <v>52</v>
-      </c>
-      <c r="U99" t="s">
-        <v>26</v>
-      </c>
-      <c r="X99">
+        <v>37</v>
+      </c>
+      <c r="P99" t="s">
+        <v>38</v>
+      </c>
+      <c r="W99" t="s">
+        <v>41</v>
+      </c>
+      <c r="X99" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB99">
         <v>7</v>
       </c>
     </row>
@@ -4617,7 +4887,7 @@
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D100">
         <v>4</v>
@@ -4634,7 +4904,7 @@
         <v>4</v>
       </c>
       <c r="C101" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -4646,15 +4916,15 @@
         <v>-32</v>
       </c>
       <c r="G101" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H101" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I101" t="s">
-        <v>90</v>
-      </c>
-      <c r="X101">
+        <v>102</v>
+      </c>
+      <c r="AB101">
         <v>7</v>
       </c>
     </row>
@@ -4666,7 +4936,7 @@
         <v>4</v>
       </c>
       <c r="C102" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -4678,33 +4948,36 @@
         <v>48</v>
       </c>
       <c r="G102" t="s">
+        <v>41</v>
+      </c>
+      <c r="H102" t="s">
+        <v>35</v>
+      </c>
+      <c r="I102" t="s">
         <v>36</v>
       </c>
-      <c r="H102" t="s">
-        <v>31</v>
-      </c>
-      <c r="I102" t="s">
-        <v>32</v>
-      </c>
       <c r="J102">
         <v>3</v>
       </c>
       <c r="K102" t="s">
-        <v>37</v>
-      </c>
-      <c r="R102" t="s">
-        <v>36</v>
-      </c>
-      <c r="S102" t="s">
-        <v>91</v>
-      </c>
-      <c r="T102" t="s">
-        <v>92</v>
-      </c>
-      <c r="U102" t="s">
-        <v>36</v>
-      </c>
-      <c r="X102">
+        <v>42</v>
+      </c>
+      <c r="P102" t="s">
+        <v>103</v>
+      </c>
+      <c r="W102" t="s">
+        <v>41</v>
+      </c>
+      <c r="X102" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y102" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB102">
         <v>6</v>
       </c>
     </row>
@@ -4716,7 +4989,7 @@
         <v>4</v>
       </c>
       <c r="C103" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D103">
         <v>2</v>
@@ -4728,33 +5001,36 @@
         <v>45</v>
       </c>
       <c r="G103" t="s">
+        <v>41</v>
+      </c>
+      <c r="H103" t="s">
+        <v>35</v>
+      </c>
+      <c r="I103" t="s">
         <v>36</v>
-      </c>
-      <c r="H103" t="s">
-        <v>31</v>
-      </c>
-      <c r="I103" t="s">
-        <v>32</v>
       </c>
       <c r="J103">
         <v>9</v>
       </c>
       <c r="K103" t="s">
-        <v>33</v>
-      </c>
-      <c r="R103" t="s">
-        <v>36</v>
-      </c>
-      <c r="S103" t="s">
-        <v>63</v>
-      </c>
-      <c r="T103" t="s">
-        <v>93</v>
-      </c>
-      <c r="U103" t="s">
-        <v>26</v>
-      </c>
-      <c r="X103">
+        <v>37</v>
+      </c>
+      <c r="P103" t="s">
+        <v>29</v>
+      </c>
+      <c r="W103" t="s">
+        <v>41</v>
+      </c>
+      <c r="X103" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB103">
         <v>6</v>
       </c>
     </row>
@@ -4766,7 +5042,7 @@
         <v>4</v>
       </c>
       <c r="C104" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -4778,12 +5054,12 @@
         <v>36</v>
       </c>
       <c r="G104" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I104" t="s">
-        <v>40</v>
-      </c>
-      <c r="X104">
+        <v>45</v>
+      </c>
+      <c r="AB104">
         <v>6</v>
       </c>
     </row>
@@ -4795,7 +5071,7 @@
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -4807,36 +5083,39 @@
         <v>39</v>
       </c>
       <c r="G105" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H105" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I105" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J105">
         <v>20</v>
       </c>
       <c r="K105" t="s">
-        <v>33</v>
-      </c>
-      <c r="R105" t="s">
-        <v>36</v>
-      </c>
-      <c r="S105" t="s">
-        <v>45</v>
-      </c>
-      <c r="T105" t="s">
-        <v>94</v>
-      </c>
-      <c r="U105" t="s">
-        <v>26</v>
-      </c>
-      <c r="V105" t="s">
-        <v>36</v>
-      </c>
-      <c r="X105">
+        <v>37</v>
+      </c>
+      <c r="P105" t="s">
+        <v>29</v>
+      </c>
+      <c r="W105" t="s">
+        <v>41</v>
+      </c>
+      <c r="X105" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA105" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB105">
         <v>8</v>
       </c>
     </row>
@@ -4848,7 +5127,7 @@
         <v>4</v>
       </c>
       <c r="C106" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -4860,36 +5139,39 @@
         <v>19</v>
       </c>
       <c r="G106" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H106" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I106" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="J106">
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>37</v>
-      </c>
-      <c r="R106" t="s">
-        <v>36</v>
-      </c>
-      <c r="S106" t="s">
-        <v>87</v>
-      </c>
-      <c r="T106" t="s">
-        <v>75</v>
-      </c>
-      <c r="U106" t="s">
-        <v>36</v>
-      </c>
-      <c r="V106" t="s">
-        <v>36</v>
-      </c>
-      <c r="X106">
+        <v>42</v>
+      </c>
+      <c r="P106" t="s">
+        <v>80</v>
+      </c>
+      <c r="W106" t="s">
+        <v>41</v>
+      </c>
+      <c r="X106" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA106" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB106">
         <v>8</v>
       </c>
     </row>
@@ -4901,7 +5183,7 @@
         <v>4</v>
       </c>
       <c r="C107" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -4913,33 +5195,36 @@
         <v>-26</v>
       </c>
       <c r="G107" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H107" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I107" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J107">
         <v>8</v>
       </c>
       <c r="K107" t="s">
-        <v>37</v>
-      </c>
-      <c r="R107" t="s">
-        <v>34</v>
-      </c>
-      <c r="S107" t="s">
-        <v>35</v>
-      </c>
-      <c r="U107" t="s">
-        <v>36</v>
-      </c>
-      <c r="V107" t="s">
-        <v>36</v>
-      </c>
-      <c r="X107">
+        <v>42</v>
+      </c>
+      <c r="P107" t="s">
+        <v>38</v>
+      </c>
+      <c r="W107" t="s">
+        <v>39</v>
+      </c>
+      <c r="X107" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA107" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB107">
         <v>7</v>
       </c>
     </row>
@@ -4951,7 +5236,7 @@
         <v>4</v>
       </c>
       <c r="C108" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D108">
         <v>2</v>
@@ -4963,30 +5248,33 @@
         <v>-34</v>
       </c>
       <c r="G108" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H108" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I108" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J108">
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>33</v>
-      </c>
-      <c r="R108" t="s">
-        <v>34</v>
-      </c>
-      <c r="S108" t="s">
-        <v>35</v>
-      </c>
-      <c r="U108" t="s">
-        <v>36</v>
-      </c>
-      <c r="X108">
+        <v>37</v>
+      </c>
+      <c r="P108" t="s">
+        <v>38</v>
+      </c>
+      <c r="W108" t="s">
+        <v>39</v>
+      </c>
+      <c r="X108" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB108">
         <v>7</v>
       </c>
     </row>
@@ -4998,7 +5286,7 @@
         <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D109">
         <v>3</v>
@@ -5010,30 +5298,33 @@
         <v>-34</v>
       </c>
       <c r="G109" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H109" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I109" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J109">
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>33</v>
-      </c>
-      <c r="R109" t="s">
-        <v>34</v>
-      </c>
-      <c r="S109" t="s">
-        <v>35</v>
-      </c>
-      <c r="U109" t="s">
-        <v>36</v>
-      </c>
-      <c r="X109">
+        <v>37</v>
+      </c>
+      <c r="P109" t="s">
+        <v>38</v>
+      </c>
+      <c r="W109" t="s">
+        <v>39</v>
+      </c>
+      <c r="X109" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB109">
         <v>7</v>
       </c>
     </row>
@@ -5045,7 +5336,7 @@
         <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D110">
         <v>4</v>
@@ -5057,30 +5348,33 @@
         <v>-34</v>
       </c>
       <c r="G110" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H110" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I110" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J110">
         <v>1</v>
       </c>
       <c r="K110" t="s">
-        <v>33</v>
-      </c>
-      <c r="R110" t="s">
-        <v>36</v>
-      </c>
-      <c r="S110" t="s">
-        <v>52</v>
-      </c>
-      <c r="U110" t="s">
-        <v>26</v>
-      </c>
-      <c r="X110">
+        <v>37</v>
+      </c>
+      <c r="P110" t="s">
+        <v>38</v>
+      </c>
+      <c r="W110" t="s">
+        <v>41</v>
+      </c>
+      <c r="X110" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB110">
         <v>7</v>
       </c>
     </row>
@@ -5092,7 +5386,7 @@
         <v>4</v>
       </c>
       <c r="C111" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -5104,18 +5398,18 @@
         <v>35</v>
       </c>
       <c r="G111" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I111" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J111">
         <v>-5</v>
       </c>
       <c r="K111" t="s">
-        <v>37</v>
-      </c>
-      <c r="X111">
+        <v>42</v>
+      </c>
+      <c r="AB111">
         <v>9</v>
       </c>
     </row>
@@ -5127,7 +5421,7 @@
         <v>4</v>
       </c>
       <c r="C112" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -5139,33 +5433,36 @@
         <v>40</v>
       </c>
       <c r="G112" t="s">
+        <v>41</v>
+      </c>
+      <c r="H112" t="s">
+        <v>35</v>
+      </c>
+      <c r="I112" t="s">
         <v>36</v>
       </c>
-      <c r="H112" t="s">
-        <v>31</v>
-      </c>
-      <c r="I112" t="s">
-        <v>32</v>
-      </c>
       <c r="J112">
         <v>2</v>
       </c>
       <c r="K112" t="s">
-        <v>37</v>
-      </c>
-      <c r="R112" t="s">
-        <v>26</v>
-      </c>
-      <c r="S112" t="s">
-        <v>57</v>
-      </c>
-      <c r="T112" t="s">
-        <v>73</v>
-      </c>
-      <c r="U112" t="s">
-        <v>36</v>
-      </c>
-      <c r="X112">
+        <v>42</v>
+      </c>
+      <c r="P112" t="s">
+        <v>69</v>
+      </c>
+      <c r="W112" t="s">
+        <v>30</v>
+      </c>
+      <c r="X112" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y112" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB112">
         <v>9</v>
       </c>
     </row>
@@ -5177,7 +5474,7 @@
         <v>4</v>
       </c>
       <c r="C113" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D113">
         <v>2</v>
@@ -5189,33 +5486,36 @@
         <v>38</v>
       </c>
       <c r="G113" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H113" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I113" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J113">
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>37</v>
-      </c>
-      <c r="R113" t="s">
-        <v>26</v>
-      </c>
-      <c r="S113" t="s">
-        <v>45</v>
-      </c>
-      <c r="T113" t="s">
-        <v>48</v>
-      </c>
-      <c r="U113" t="s">
-        <v>36</v>
-      </c>
-      <c r="X113">
+        <v>42</v>
+      </c>
+      <c r="P113" t="s">
+        <v>29</v>
+      </c>
+      <c r="W113" t="s">
+        <v>30</v>
+      </c>
+      <c r="X113" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y113" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB113">
         <v>9</v>
       </c>
     </row>
@@ -5227,7 +5527,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D114">
         <v>3</v>
@@ -5239,33 +5539,36 @@
         <v>38</v>
       </c>
       <c r="G114" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H114" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I114" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>37</v>
-      </c>
-      <c r="R114" t="s">
-        <v>36</v>
-      </c>
-      <c r="S114" t="s">
-        <v>91</v>
-      </c>
-      <c r="T114" t="s">
-        <v>96</v>
-      </c>
-      <c r="U114" t="s">
-        <v>26</v>
-      </c>
-      <c r="X114">
+        <v>42</v>
+      </c>
+      <c r="P114" t="s">
+        <v>80</v>
+      </c>
+      <c r="W114" t="s">
+        <v>41</v>
+      </c>
+      <c r="X114" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y114" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB114">
         <v>9</v>
       </c>
     </row>
@@ -5277,7 +5580,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D115">
         <v>4</v>
@@ -5289,33 +5592,36 @@
         <v>38</v>
       </c>
       <c r="G115" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H115" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I115" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J115">
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>37</v>
-      </c>
-      <c r="R115" t="s">
-        <v>26</v>
-      </c>
-      <c r="S115" t="s">
-        <v>45</v>
-      </c>
-      <c r="T115" t="s">
-        <v>85</v>
-      </c>
-      <c r="U115" t="s">
-        <v>36</v>
-      </c>
-      <c r="X115">
+        <v>42</v>
+      </c>
+      <c r="P115" t="s">
+        <v>29</v>
+      </c>
+      <c r="W115" t="s">
+        <v>30</v>
+      </c>
+      <c r="X115" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y115" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z115" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB115">
         <v>9</v>
       </c>
     </row>
@@ -5327,7 +5633,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -5339,30 +5645,30 @@
         <v>-38</v>
       </c>
       <c r="G116" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H116" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I116" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J116">
         <v>2</v>
       </c>
       <c r="K116" t="s">
-        <v>33</v>
-      </c>
-      <c r="R116" t="s">
-        <v>36</v>
-      </c>
-      <c r="S116" t="s">
-        <v>97</v>
-      </c>
-      <c r="U116" t="s">
-        <v>36</v>
-      </c>
-      <c r="X116">
+        <v>37</v>
+      </c>
+      <c r="W116" t="s">
+        <v>41</v>
+      </c>
+      <c r="X116" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z116" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB116">
         <v>8</v>
       </c>
     </row>
@@ -5374,7 +5680,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D117">
         <v>2</v>
@@ -5386,30 +5692,33 @@
         <v>-40</v>
       </c>
       <c r="G117" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H117" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I117" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J117">
         <v>4</v>
       </c>
       <c r="K117" t="s">
-        <v>37</v>
-      </c>
-      <c r="R117" t="s">
-        <v>36</v>
-      </c>
-      <c r="S117" t="s">
-        <v>52</v>
-      </c>
-      <c r="U117" t="s">
-        <v>26</v>
-      </c>
-      <c r="X117">
+        <v>42</v>
+      </c>
+      <c r="P117" t="s">
+        <v>38</v>
+      </c>
+      <c r="W117" t="s">
+        <v>41</v>
+      </c>
+      <c r="X117" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z117" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB117">
         <v>8</v>
       </c>
     </row>
@@ -5421,7 +5730,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D118">
         <v>3</v>
@@ -5433,18 +5742,18 @@
         <v>-44</v>
       </c>
       <c r="G118" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I118" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J118">
         <v>5</v>
       </c>
       <c r="K118" t="s">
-        <v>37</v>
-      </c>
-      <c r="X118">
+        <v>42</v>
+      </c>
+      <c r="AB118">
         <v>8</v>
       </c>
     </row>
@@ -5456,7 +5765,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -5468,30 +5777,33 @@
         <v>-49</v>
       </c>
       <c r="G119" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H119" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I119" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J119">
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>33</v>
-      </c>
-      <c r="R119" t="s">
-        <v>34</v>
-      </c>
-      <c r="S119" t="s">
-        <v>35</v>
-      </c>
-      <c r="U119" t="s">
-        <v>36</v>
-      </c>
-      <c r="X119">
+        <v>37</v>
+      </c>
+      <c r="P119" t="s">
+        <v>38</v>
+      </c>
+      <c r="W119" t="s">
+        <v>39</v>
+      </c>
+      <c r="X119" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z119" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB119">
         <v>8</v>
       </c>
     </row>
@@ -5503,7 +5815,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D120">
         <v>2</v>
@@ -5515,30 +5827,33 @@
         <v>-49</v>
       </c>
       <c r="G120" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H120" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I120" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J120">
         <v>15</v>
       </c>
       <c r="K120" t="s">
-        <v>37</v>
-      </c>
-      <c r="R120" t="s">
-        <v>26</v>
-      </c>
-      <c r="S120" t="s">
-        <v>52</v>
-      </c>
-      <c r="U120" t="s">
-        <v>36</v>
-      </c>
-      <c r="X120">
+        <v>42</v>
+      </c>
+      <c r="P120" t="s">
+        <v>38</v>
+      </c>
+      <c r="W120" t="s">
+        <v>30</v>
+      </c>
+      <c r="X120" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z120" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB120">
         <v>8</v>
       </c>
     </row>
@@ -5550,7 +5865,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -5562,30 +5877,33 @@
         <v>36</v>
       </c>
       <c r="G121" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H121" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I121" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J121">
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>33</v>
-      </c>
-      <c r="R121" t="s">
-        <v>26</v>
-      </c>
-      <c r="S121" t="s">
-        <v>52</v>
-      </c>
-      <c r="U121" t="s">
-        <v>36</v>
-      </c>
-      <c r="X121">
+        <v>37</v>
+      </c>
+      <c r="P121" t="s">
+        <v>38</v>
+      </c>
+      <c r="W121" t="s">
+        <v>30</v>
+      </c>
+      <c r="X121" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z121" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB121">
         <v>8</v>
       </c>
     </row>
@@ -5597,7 +5915,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D122">
         <v>2</v>
@@ -5609,30 +5927,33 @@
         <v>36</v>
       </c>
       <c r="G122" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H122" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I122" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J122">
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>33</v>
-      </c>
-      <c r="R122" t="s">
-        <v>26</v>
-      </c>
-      <c r="S122" t="s">
-        <v>52</v>
-      </c>
-      <c r="U122" t="s">
-        <v>36</v>
-      </c>
-      <c r="X122">
+        <v>37</v>
+      </c>
+      <c r="P122" t="s">
+        <v>38</v>
+      </c>
+      <c r="W122" t="s">
+        <v>30</v>
+      </c>
+      <c r="X122" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z122" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB122">
         <v>8</v>
       </c>
     </row>
@@ -5644,7 +5965,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -5656,30 +5977,33 @@
         <v>36</v>
       </c>
       <c r="G123" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H123" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I123" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J123">
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>33</v>
-      </c>
-      <c r="R123" t="s">
-        <v>34</v>
-      </c>
-      <c r="S123" t="s">
-        <v>35</v>
-      </c>
-      <c r="U123" t="s">
-        <v>36</v>
-      </c>
-      <c r="X123">
+        <v>37</v>
+      </c>
+      <c r="P123" t="s">
+        <v>38</v>
+      </c>
+      <c r="W123" t="s">
+        <v>39</v>
+      </c>
+      <c r="X123" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z123" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB123">
         <v>8</v>
       </c>
     </row>
